--- a/game28/web.xlsx
+++ b/game28/web.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="13440" windowHeight="5730"/>
+    <workbookView windowWidth="15000" windowHeight="7620" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="14" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="15" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="13" r:id="rId3"/>
+    <sheet name="Sheet5" sheetId="10" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
   <si>
     <t>domain</t>
   </si>
@@ -37,46 +38,146 @@
     <t>color</t>
   </si>
   <si>
+    <t>color2</t>
+  </si>
+  <si>
+    <t>sec.wuuui.top</t>
+  </si>
+  <si>
+    <t>#957aa9</t>
+  </si>
+  <si>
+    <t>sec.flowflux.cloud</t>
+  </si>
+  <si>
+    <t>#33325d</t>
+  </si>
+  <si>
+    <t>spuddles.fun</t>
+  </si>
+  <si>
+    <t>#707899</t>
+  </si>
+  <si>
+    <t>moilfuns.fun</t>
+  </si>
+  <si>
+    <t>#70c588</t>
+  </si>
+  <si>
     <t>color1</t>
   </si>
   <si>
-    <t>color2</t>
-  </si>
-  <si>
     <t>info</t>
   </si>
   <si>
     <t>json</t>
   </si>
   <si>
-    <t>frostspike.com</t>
-  </si>
-  <si>
-    <t>#ffd9a3</t>
-  </si>
-  <si>
-    <t>warpblade.com</t>
-  </si>
-  <si>
-    <t>#f597ba</t>
-  </si>
-  <si>
-    <t>ghostlurk.com</t>
-  </si>
-  <si>
-    <t>#b8f500</t>
-  </si>
-  <si>
-    <t>emberlurk.com</t>
-  </si>
-  <si>
-    <t>#bdd0c4</t>
-  </si>
-  <si>
-    <t>runepeak.com</t>
-  </si>
-  <si>
-    <t>#957aa9</t>
+    <t>lagoonsea.com</t>
+  </si>
+  <si>
+    <t>#ffc408</t>
+  </si>
+  <si>
+    <t>navyseas.com</t>
+  </si>
+  <si>
+    <t>#6b496a</t>
+  </si>
+  <si>
+    <t>sapphsea.com</t>
+  </si>
+  <si>
+    <t>#e6e3c3</t>
+  </si>
+  <si>
+    <t>skyssea.com</t>
+  </si>
+  <si>
+    <t>#606da1</t>
+  </si>
+  <si>
+    <t>sunseabc.com</t>
+  </si>
+  <si>
+    <t>#ee819e</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF175CEB"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sec</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF175CEB"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.desertwoodrat.com</t>
+    </r>
+  </si>
+  <si>
+    <t>#fdf4e3</t>
+  </si>
+  <si>
+    <t>#7c8d99</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF175CEB"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sec</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF175CEB"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.desertskink.com</t>
+    </r>
+  </si>
+  <si>
+    <t>#e1e6e9</t>
+  </si>
+  <si>
+    <t>#a35e5e</t>
+  </si>
+  <si>
+    <t>sec.eunoias.cloud</t>
+  </si>
+  <si>
+    <t>#f0ff31</t>
+  </si>
+  <si>
+    <t>sec.uminous.top</t>
+  </si>
+  <si>
+    <t>#27456c</t>
+  </si>
+  <si>
+    <t>sec.nebulous.top</t>
+  </si>
+  <si>
+    <t>#98b0ca</t>
   </si>
 </sst>
 </file>
@@ -89,12 +190,177 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="32">
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF2972F4"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFCE9178"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF175CEB"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF1450B8"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -102,125 +368,6 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF2972F4"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -274,8 +421,16 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF175CEB"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="39">
+  <fills count="52">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -284,25 +439,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFD9A3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF597BA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8F500"/>
+        <fgColor rgb="FFF0FF31"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27456C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF98B0CA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7C8D99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1E6E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA35E5E"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -314,12 +487,72 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC408"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6090B8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6B496A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6E3C3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF606DA1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE819E"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF957AA9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA61B29"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33325D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF707899"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70C588"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -505,12 +738,21 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFE3E4E6"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -613,179 +855,244 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="38" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="32">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -839,7 +1146,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -849,9 +1156,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="WPS">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -859,39 +1166,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4874CB"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EE822F"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="F2BA02"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="75BD42"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="30C0B4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="E54C5E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0026E5"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="7E1FAD"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="WPS">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -961,242 +1268,288 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="WPS">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumOff val="17500"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:hueOff val="-2520000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:gradFill>
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="phClr">
-                  <a:hueOff val="-4200000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="phClr"/>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="2700000" scaled="1"/>
-          </a:gradFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:schemeClr val="phClr">
-                <a:alpha val="60000"/>
-              </a:schemeClr>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="5"/>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="27.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:6">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="B2" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="C2" s="26"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" ht="14.25" spans="1:6">
-      <c r="A2" s="3" t="s">
+      <c r="B3" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C3" s="26"/>
+    </row>
+    <row r="4" ht="15" spans="1:7">
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+    </row>
+    <row r="5" ht="15" spans="1:7">
+      <c r="A5" s="22"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
+    </row>
+    <row r="6" ht="15" spans="1:7">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="F16" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="2">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" ht="14.25" spans="1:6">
-      <c r="A3" s="3" t="s">
+      <c r="G16" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="5" t="s">
+    </row>
+    <row r="17" spans="6:7">
+      <c r="F17" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="2">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" ht="14.25" spans="1:6">
-      <c r="A4" s="3" t="s">
+      <c r="G17" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="2">
-        <v>3</v>
-      </c>
-      <c r="F4" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" ht="14.25" spans="1:6">
-      <c r="A5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="2">
-        <v>4</v>
-      </c>
-      <c r="F5" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" ht="14.25" spans="1:6">
-      <c r="A6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="2">
-        <v>5</v>
-      </c>
-      <c r="F6" s="2">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <hyperlinks>
+    <hyperlink ref="F16" r:id="rId1" display="spuddles.fun"/>
+    <hyperlink ref="F17" r:id="rId2" display="moilfuns.fun"/>
+    <hyperlink ref="A6" r:id="rId3" tooltip="https://jentacul.com"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -1204,11 +1557,133 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="18.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="18"/>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="18"/>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="18"/>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" ht="15" spans="1:6">
+      <c r="A5" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="18"/>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5" s="15">
+        <v>5</v>
+      </c>
+      <c r="F5" s="22"/>
+    </row>
+    <row r="6" ht="15" spans="1:6">
+      <c r="A6" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="22"/>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6" s="15">
+        <v>5</v>
+      </c>
+      <c r="F6" s="22"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="D7" s="15"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="D8" s="15"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="D9" s="15"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="D10" s="15"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="D11" s="15"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="D12" s="15"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="lagoonsea.com" tooltip="https://lagoonsea.com"/>
+    <hyperlink ref="A3" r:id="rId2" display="navyseas.com" tooltip="https://navyseas.com"/>
+    <hyperlink ref="A4" r:id="rId3" display="sapphsea.com" tooltip="https://sapphsea.com"/>
+    <hyperlink ref="A5" r:id="rId4" display="skyssea.com" tooltip="https://skyssea.com"/>
+    <hyperlink ref="A6" r:id="rId5" display="sunseabc.com" tooltip="https://sunseabc.com"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -1216,11 +1691,193 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="26.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="12"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="5"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A6" r:id="rId1"/>
+    <hyperlink ref="A2" r:id="rId2" display="sec.desertwoodrat.com" tooltip="http://desertwoodrat.com"/>
+    <hyperlink ref="A3" r:id="rId3" display="sec.desertskink.com" tooltip="http://desertskink.com"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="5"/>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="C7" s="6"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A5" r:id="rId1"/>
+    <hyperlink ref="A6" r:id="rId2"/>
+    <hyperlink ref="B5" r:id="rId1"/>
+    <hyperlink ref="C5" r:id="rId1"/>
+    <hyperlink ref="D5" r:id="rId1"/>
+    <hyperlink ref="E5" r:id="rId1"/>
+    <hyperlink ref="B6" r:id="rId2"/>
+    <hyperlink ref="C6" r:id="rId2"/>
+    <hyperlink ref="D6" r:id="rId2"/>
+    <hyperlink ref="E6" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>